--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$7</f>
+              <f>'DailyProfit'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$7</f>
+              <f>'DailyProfit'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$7</f>
+              <f>'DailyProfit'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$7</f>
+              <f>'DailyProfit'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$7</f>
+              <f>'DailyProfit'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$7</f>
+              <f>'DailyProfit'!$F$2:$F$8</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$7</f>
+              <f>'DailyProfit'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$7</f>
+              <f>'DailyProfit'!$G$2:$G$8</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$7</f>
+              <f>'DailyProfit'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$7</f>
+              <f>'DailyProfit'!$H$2:$H$8</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1398,7 +1398,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -1429,6 +1429,40 @@
       </c>
       <c r="J7" s="11" t="n">
         <v>212416</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>352298</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>829549</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>6824073</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>0.004697306666666666</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.01106065333333333</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>0.09098763999999999</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>139882</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>352298</v>
       </c>
     </row>
   </sheetData>
@@ -1506,7 +1540,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1561,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>212416</v>
+        <v>352298</v>
       </c>
     </row>
     <row r="5">
@@ -1537,7 +1571,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>477251</v>
+        <v>829549</v>
       </c>
     </row>
     <row r="6">
@@ -1547,7 +1581,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>6471775</v>
+        <v>6824073</v>
       </c>
     </row>
     <row r="7">
@@ -1557,7 +1591,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.002832213333333333</v>
+        <v>0.004697306666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1567,7 +1601,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.006363346666666667</v>
+        <v>0.01106065333333333</v>
       </c>
     </row>
     <row r="9">
@@ -1577,7 +1611,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.08629033333333333</v>
+        <v>0.09098763999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1587,7 +1621,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>239722.1666666667</v>
+        <v>255804.4285714286</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$8</f>
+              <f>'DailyProfit'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$8</f>
+              <f>'DailyProfit'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$8</f>
+              <f>'DailyProfit'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$8</f>
+              <f>'DailyProfit'!$D$2:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$8</f>
+              <f>'DailyProfit'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$8</f>
+              <f>'DailyProfit'!$F$2:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$8</f>
+              <f>'DailyProfit'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$8</f>
+              <f>'DailyProfit'!$G$2:$G$9</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$8</f>
+              <f>'DailyProfit'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$8</f>
+              <f>'DailyProfit'!$H$2:$H$9</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1432,7 +1432,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
@@ -1463,6 +1463,40 @@
       </c>
       <c r="J8" s="11" t="n">
         <v>352298</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>272682</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>1700595</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>136341</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>850297.5</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>-352243</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>-5123478</v>
       </c>
     </row>
   </sheetData>
@@ -1540,7 +1574,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1585,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1561,7 +1595,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>352298</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -1571,7 +1605,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>829549</v>
+        <v>272682</v>
       </c>
     </row>
     <row r="6">
@@ -1581,7 +1615,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>6824073</v>
+        <v>1700595</v>
       </c>
     </row>
     <row r="7">
@@ -1591,7 +1625,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.004697306666666666</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="8">
@@ -1601,7 +1635,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01106065333333333</v>
+        <v>136341</v>
       </c>
     </row>
     <row r="9">
@@ -1611,7 +1645,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.09098763999999999</v>
+        <v>850297.5</v>
       </c>
     </row>
     <row r="10">
@@ -1621,7 +1655,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>255804.4285714286</v>
+        <v>223835.75</v>
       </c>
     </row>
     <row r="11">
@@ -1654,7 +1688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1699,7 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>113683</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -1685,7 +1719,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>0</v>
+        <v>-0.7507947233272563</v>
       </c>
     </row>
   </sheetData>

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$9</f>
+              <f>'DailyProfit'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$9</f>
+              <f>'DailyProfit'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$9</f>
+              <f>'DailyProfit'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$9</f>
+              <f>'DailyProfit'!$D$2:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$9</f>
+              <f>'DailyProfit'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$9</f>
+              <f>'DailyProfit'!$F$2:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$9</f>
+              <f>'DailyProfit'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$9</f>
+              <f>'DailyProfit'!$G$2:$G$10</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$9</f>
+              <f>'DailyProfit'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$9</f>
+              <f>'DailyProfit'!$H$2:$H$10</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1466,7 +1466,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
@@ -1497,6 +1497,40 @@
       </c>
       <c r="J9" s="11" t="n">
         <v>-5123478</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>430953</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>2509005</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>215476.5</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>1254502.5</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>808410</v>
       </c>
     </row>
   </sheetData>
@@ -1574,7 +1608,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1629,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -1605,7 +1639,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>272682</v>
+        <v>430953</v>
       </c>
     </row>
     <row r="6">
@@ -1615,7 +1649,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>1700595</v>
+        <v>2509005</v>
       </c>
     </row>
     <row r="7">
@@ -1625,7 +1659,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="8">
@@ -1635,7 +1669,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>136341</v>
+        <v>215476.5</v>
       </c>
     </row>
     <row r="9">
@@ -1645,7 +1679,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>850297.5</v>
+        <v>1254502.5</v>
       </c>
     </row>
     <row r="10">
@@ -1655,7 +1689,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>223835.75</v>
+        <v>198971.4444444444</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$10</f>
+              <f>'DailyProfit'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$10</f>
+              <f>'DailyProfit'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$10</f>
+              <f>'DailyProfit'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$10</f>
+              <f>'DailyProfit'!$D$2:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$10</f>
+              <f>'DailyProfit'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$10</f>
+              <f>'DailyProfit'!$F$2:$F$11</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$10</f>
+              <f>'DailyProfit'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$10</f>
+              <f>'DailyProfit'!$G$2:$G$11</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$10</f>
+              <f>'DailyProfit'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$10</f>
+              <f>'DailyProfit'!$H$2:$H$11</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1500,7 +1500,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
@@ -1531,6 +1531,40 @@
       </c>
       <c r="J10" s="11" t="n">
         <v>808410</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>244944</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>2753949</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>122472</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>1376974.5</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>244944</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1642,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1673,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>430953</v>
+        <v>244944</v>
       </c>
     </row>
     <row r="6">
@@ -1649,7 +1683,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>2509005</v>
+        <v>2753949</v>
       </c>
     </row>
     <row r="7">
@@ -1669,7 +1703,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>215476.5</v>
+        <v>122472</v>
       </c>
     </row>
     <row r="9">
@@ -1679,7 +1713,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1254502.5</v>
+        <v>1376974.5</v>
       </c>
     </row>
     <row r="10">
@@ -1689,7 +1723,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>198971.4444444444</v>
+        <v>179080</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$11</f>
+              <f>'DailyProfit'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$11</f>
+              <f>'DailyProfit'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$11</f>
+              <f>'DailyProfit'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$11</f>
+              <f>'DailyProfit'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$11</f>
+              <f>'DailyProfit'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$11</f>
+              <f>'DailyProfit'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$11</f>
+              <f>'DailyProfit'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$11</f>
+              <f>'DailyProfit'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$11</f>
+              <f>'DailyProfit'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$11</f>
+              <f>'DailyProfit'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1534,7 +1534,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
@@ -1565,6 +1565,40 @@
       </c>
       <c r="J11" s="11" t="n">
         <v>244944</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>134453</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>2888402</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>8882926</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>0.001600630952380952</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0.03438573809523809</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0.1057491190476191</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>134396</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>6128977</v>
       </c>
     </row>
   </sheetData>
@@ -1642,7 +1676,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1687,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>0</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="4">
@@ -1663,7 +1697,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>57</v>
+        <v>134453</v>
       </c>
     </row>
     <row r="5">
@@ -1673,7 +1707,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>244944</v>
+        <v>2888402</v>
       </c>
     </row>
     <row r="6">
@@ -1683,7 +1717,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>2753949</v>
+        <v>8882926</v>
       </c>
     </row>
     <row r="7">
@@ -1693,7 +1727,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>28.5</v>
+        <v>0.001600630952380952</v>
       </c>
     </row>
     <row r="8">
@@ -1703,7 +1737,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>122472</v>
+        <v>0.03438573809523809</v>
       </c>
     </row>
     <row r="9">
@@ -1713,7 +1747,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1376974.5</v>
+        <v>0.1057491190476191</v>
       </c>
     </row>
     <row r="10">
@@ -1723,7 +1757,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>179080</v>
+        <v>175023</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$12</f>
+              <f>'DailyProfit'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$12</f>
+              <f>'DailyProfit'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$12</f>
+              <f>'DailyProfit'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$12</f>
+              <f>'DailyProfit'!$D$2:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$12</f>
+              <f>'DailyProfit'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$12</f>
+              <f>'DailyProfit'!$F$2:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$12</f>
+              <f>'DailyProfit'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$12</f>
+              <f>'DailyProfit'!$G$2:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$12</f>
+              <f>'DailyProfit'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$12</f>
+              <f>'DailyProfit'!$H$2:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1568,7 +1568,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
@@ -1599,6 +1599,40 @@
       </c>
       <c r="J12" s="11" t="n">
         <v>6128977</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>140205</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>3028607</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>9023131</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0.001669107142857143</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.03605484523809524</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0.1074182261904762</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>5752</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>140205</v>
       </c>
     </row>
   </sheetData>
@@ -1676,7 +1710,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1731,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>134453</v>
+        <v>140205</v>
       </c>
     </row>
     <row r="5">
@@ -1707,7 +1741,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2888402</v>
+        <v>3028607</v>
       </c>
     </row>
     <row r="6">
@@ -1717,7 +1751,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>8882926</v>
+        <v>9023131</v>
       </c>
     </row>
     <row r="7">
@@ -1727,7 +1761,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001600630952380952</v>
+        <v>0.001669107142857143</v>
       </c>
     </row>
     <row r="8">
@@ -1737,7 +1771,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.03438573809523809</v>
+        <v>0.03605484523809524</v>
       </c>
     </row>
     <row r="9">
@@ -1747,7 +1781,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1057491190476191</v>
+        <v>0.1074182261904762</v>
       </c>
     </row>
     <row r="10">
@@ -1757,7 +1791,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>175023</v>
+        <v>172121.5</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$13</f>
+              <f>'DailyProfit'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$13</f>
+              <f>'DailyProfit'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$13</f>
+              <f>'DailyProfit'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$13</f>
+              <f>'DailyProfit'!$D$2:$D$14</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$13</f>
+              <f>'DailyProfit'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$13</f>
+              <f>'DailyProfit'!$F$2:$F$14</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$13</f>
+              <f>'DailyProfit'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$13</f>
+              <f>'DailyProfit'!$G$2:$G$14</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$13</f>
+              <f>'DailyProfit'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$13</f>
+              <f>'DailyProfit'!$H$2:$H$14</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1602,7 +1602,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
@@ -1633,6 +1633,40 @@
       </c>
       <c r="J13" s="11" t="n">
         <v>140205</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>233670</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>3262277</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>9256801</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>11100</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>0.002105135135135135</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.02938988288288288</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0.08339460360360361</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>93465</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>233670</v>
       </c>
     </row>
   </sheetData>
@@ -1710,7 +1744,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1755,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>8400</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="4">
@@ -1731,7 +1765,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>140205</v>
+        <v>233670</v>
       </c>
     </row>
     <row r="5">
@@ -1741,7 +1775,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>3028607</v>
+        <v>3262277</v>
       </c>
     </row>
     <row r="6">
@@ -1751,7 +1785,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>9023131</v>
+        <v>9256801</v>
       </c>
     </row>
     <row r="7">
@@ -1761,7 +1795,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001669107142857143</v>
+        <v>0.002105135135135135</v>
       </c>
     </row>
     <row r="8">
@@ -1771,7 +1805,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.03605484523809524</v>
+        <v>0.02938988288288288</v>
       </c>
     </row>
     <row r="9">
@@ -1781,7 +1815,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1074182261904762</v>
+        <v>0.08339460360360361</v>
       </c>
     </row>
     <row r="10">
@@ -1791,7 +1825,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>172121.5</v>
+        <v>176856</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$14</f>
+              <f>'DailyProfit'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$14</f>
+              <f>'DailyProfit'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$14</f>
+              <f>'DailyProfit'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$14</f>
+              <f>'DailyProfit'!$D$2:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$14</f>
+              <f>'DailyProfit'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$14</f>
+              <f>'DailyProfit'!$F$2:$F$15</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$14</f>
+              <f>'DailyProfit'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$14</f>
+              <f>'DailyProfit'!$G$2:$G$15</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$14</f>
+              <f>'DailyProfit'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$14</f>
+              <f>'DailyProfit'!$H$2:$H$15</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1636,7 +1636,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
@@ -1667,6 +1667,40 @@
       </c>
       <c r="J14" s="11" t="n">
         <v>233670</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>281378</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>3543655</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>9538179</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>11100</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0.002534936936936937</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.03192481981981982</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0.08592954054054054</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>47708</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>281378</v>
       </c>
     </row>
   </sheetData>
@@ -1744,7 +1778,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1799,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>233670</v>
+        <v>281378</v>
       </c>
     </row>
     <row r="5">
@@ -1775,7 +1809,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>3262277</v>
+        <v>3543655</v>
       </c>
     </row>
     <row r="6">
@@ -1785,7 +1819,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>9256801</v>
+        <v>9538179</v>
       </c>
     </row>
     <row r="7">
@@ -1795,7 +1829,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.002105135135135135</v>
+        <v>0.002534936936936937</v>
       </c>
     </row>
     <row r="8">
@@ -1805,7 +1839,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02938988288288288</v>
+        <v>0.03192481981981982</v>
       </c>
     </row>
     <row r="9">
@@ -1815,7 +1849,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.08339460360360361</v>
+        <v>0.08592954054054054</v>
       </c>
     </row>
     <row r="10">
@@ -1825,7 +1859,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>176856</v>
+        <v>184321.8571428571</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$15</f>
+              <f>'DailyProfit'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$15</f>
+              <f>'DailyProfit'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$15</f>
+              <f>'DailyProfit'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$15</f>
+              <f>'DailyProfit'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$15</f>
+              <f>'DailyProfit'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$15</f>
+              <f>'DailyProfit'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$15</f>
+              <f>'DailyProfit'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$15</f>
+              <f>'DailyProfit'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$15</f>
+              <f>'DailyProfit'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$15</f>
+              <f>'DailyProfit'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1670,7 +1670,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
@@ -1701,6 +1701,40 @@
       </c>
       <c r="J15" s="11" t="n">
         <v>281378</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>200614</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>3744269</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>9738793</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>11100</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>0.001807333333333333</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.03373215315315315</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>0.08773687387387387</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>-80764</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>200614</v>
       </c>
     </row>
   </sheetData>
@@ -1778,7 +1812,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1833,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>281378</v>
+        <v>200614</v>
       </c>
     </row>
     <row r="5">
@@ -1809,7 +1843,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>3543655</v>
+        <v>3744269</v>
       </c>
     </row>
     <row r="6">
@@ -1819,7 +1853,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>9538179</v>
+        <v>9738793</v>
       </c>
     </row>
     <row r="7">
@@ -1829,7 +1863,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.002534936936936937</v>
+        <v>0.001807333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -1839,7 +1873,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.03192481981981982</v>
+        <v>0.03373215315315315</v>
       </c>
     </row>
     <row r="9">
@@ -1849,7 +1883,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.08592954054054054</v>
+        <v>0.08773687387387387</v>
       </c>
     </row>
     <row r="10">
@@ -1859,7 +1893,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>184321.8571428571</v>
+        <v>185408</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$16</f>
+              <f>'DailyProfit'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$16</f>
+              <f>'DailyProfit'!$B$2:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$16</f>
+              <f>'DailyProfit'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$16</f>
+              <f>'DailyProfit'!$D$2:$D$17</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$16</f>
+              <f>'DailyProfit'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$16</f>
+              <f>'DailyProfit'!$F$2:$F$17</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$16</f>
+              <f>'DailyProfit'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$16</f>
+              <f>'DailyProfit'!$G$2:$G$17</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$16</f>
+              <f>'DailyProfit'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$16</f>
+              <f>'DailyProfit'!$H$2:$H$17</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1704,7 +1704,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
@@ -1735,6 +1735,40 @@
       </c>
       <c r="J16" s="11" t="n">
         <v>200614</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>148568</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>3892837</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>9887361</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>11100</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0.001338450450450451</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.0350706036036036</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>0.08907532432432433</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>-52046</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>148568</v>
       </c>
     </row>
   </sheetData>
@@ -1812,7 +1846,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1867,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>200614</v>
+        <v>148568</v>
       </c>
     </row>
     <row r="5">
@@ -1843,7 +1877,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>3744269</v>
+        <v>3892837</v>
       </c>
     </row>
     <row r="6">
@@ -1853,7 +1887,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>9738793</v>
+        <v>9887361</v>
       </c>
     </row>
     <row r="7">
@@ -1863,7 +1897,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001807333333333333</v>
+        <v>0.001338450450450451</v>
       </c>
     </row>
     <row r="8">
@@ -1873,7 +1907,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.03373215315315315</v>
+        <v>0.0350706036036036</v>
       </c>
     </row>
     <row r="9">
@@ -1883,7 +1917,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.08773687387387387</v>
+        <v>0.08907532432432433</v>
       </c>
     </row>
     <row r="10">
@@ -1893,7 +1927,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>185408</v>
+        <v>183105.5</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$17</f>
+              <f>'DailyProfit'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$17</f>
+              <f>'DailyProfit'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$17</f>
+              <f>'DailyProfit'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$17</f>
+              <f>'DailyProfit'!$D$2:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$17</f>
+              <f>'DailyProfit'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$17</f>
+              <f>'DailyProfit'!$F$2:$F$18</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$17</f>
+              <f>'DailyProfit'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$17</f>
+              <f>'DailyProfit'!$G$2:$G$18</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$17</f>
+              <f>'DailyProfit'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$17</f>
+              <f>'DailyProfit'!$H$2:$H$18</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1738,7 +1738,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
@@ -1769,6 +1769,40 @@
       </c>
       <c r="J17" s="11" t="n">
         <v>148568</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>351983</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>4244820</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>10239344</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>12600</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>0.002793515873015873</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.03368904761904762</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>0.08126463492063492</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>203415</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>351983</v>
       </c>
     </row>
   </sheetData>
@@ -1846,7 +1880,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1891,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>11100</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="4">
@@ -1867,7 +1901,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>148568</v>
+        <v>351983</v>
       </c>
     </row>
     <row r="5">
@@ -1877,7 +1911,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>3892837</v>
+        <v>4244820</v>
       </c>
     </row>
     <row r="6">
@@ -1887,7 +1921,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>9887361</v>
+        <v>10239344</v>
       </c>
     </row>
     <row r="7">
@@ -1897,7 +1931,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001338450450450451</v>
+        <v>0.002793515873015873</v>
       </c>
     </row>
     <row r="8">
@@ -1907,7 +1941,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.0350706036036036</v>
+        <v>0.03368904761904762</v>
       </c>
     </row>
     <row r="9">
@@ -1917,7 +1951,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.08907532432432433</v>
+        <v>0.08126463492063492</v>
       </c>
     </row>
     <row r="10">
@@ -1927,7 +1961,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>183105.5</v>
+        <v>193039.4705882353</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$18</f>
+              <f>'DailyProfit'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$18</f>
+              <f>'DailyProfit'!$B$2:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$18</f>
+              <f>'DailyProfit'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$18</f>
+              <f>'DailyProfit'!$D$2:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$18</f>
+              <f>'DailyProfit'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$18</f>
+              <f>'DailyProfit'!$F$2:$F$19</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$18</f>
+              <f>'DailyProfit'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$18</f>
+              <f>'DailyProfit'!$G$2:$G$19</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$18</f>
+              <f>'DailyProfit'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$18</f>
+              <f>'DailyProfit'!$H$2:$H$19</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1772,7 +1772,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
@@ -1803,6 +1803,40 @@
       </c>
       <c r="J18" s="11" t="n">
         <v>351983</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>397104</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>4817700</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>10812224</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>12600</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>0.003151619047619048</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0.03823571428571428</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>0.08581130158730159</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>45121</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>572880</v>
       </c>
     </row>
   </sheetData>
@@ -1880,7 +1914,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1935,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>351983</v>
+        <v>397104</v>
       </c>
     </row>
     <row r="5">
@@ -1911,7 +1945,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>4244820</v>
+        <v>4817700</v>
       </c>
     </row>
     <row r="6">
@@ -1921,7 +1955,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>10239344</v>
+        <v>10812224</v>
       </c>
     </row>
     <row r="7">
@@ -1931,7 +1965,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.002793515873015873</v>
+        <v>0.003151619047619048</v>
       </c>
     </row>
     <row r="8">
@@ -1941,7 +1975,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.03368904761904762</v>
+        <v>0.03823571428571428</v>
       </c>
     </row>
     <row r="9">
@@ -1951,7 +1985,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.08126463492063492</v>
+        <v>0.08581130158730159</v>
       </c>
     </row>
     <row r="10">
@@ -1961,7 +1995,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>193039.4705882353</v>
+        <v>204376.3888888889</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$19</f>
+              <f>'DailyProfit'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$19</f>
+              <f>'DailyProfit'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$19</f>
+              <f>'DailyProfit'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$19</f>
+              <f>'DailyProfit'!$D$2:$D$20</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$19</f>
+              <f>'DailyProfit'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$19</f>
+              <f>'DailyProfit'!$F$2:$F$20</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$19</f>
+              <f>'DailyProfit'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$19</f>
+              <f>'DailyProfit'!$G$2:$G$20</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$19</f>
+              <f>'DailyProfit'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$19</f>
+              <f>'DailyProfit'!$H$2:$H$20</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1806,7 +1806,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -1837,6 +1837,40 @@
       </c>
       <c r="J19" s="11" t="n">
         <v>572880</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>137716817</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>34429204.25</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>137319713</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>-10812165</v>
       </c>
     </row>
   </sheetData>
@@ -1914,7 +1948,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1959,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>12600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1935,7 +1969,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>397104</v>
+        <v>137716817</v>
       </c>
     </row>
     <row r="5">
@@ -1945,7 +1979,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>4817700</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1955,7 +1989,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>10812224</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -1965,7 +1999,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.003151619047619048</v>
+        <v>34429204.25</v>
       </c>
     </row>
     <row r="8">
@@ -1975,7 +2009,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.03823571428571428</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
@@ -1985,7 +2019,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.08581130158730159</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="10">
@@ -1995,7 +2029,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>204376.3888888889</v>
+        <v>7441873.263157895</v>
       </c>
     </row>
     <row r="11">
@@ -2006,7 +2040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2051,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>406810</v>
+        <v>137716817</v>
       </c>
     </row>
     <row r="13">
@@ -2059,7 +2093,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>-0.7507947233272563</v>
+        <v>-0.9999945432133112</v>
       </c>
     </row>
   </sheetData>

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$20</f>
+              <f>'DailyProfit'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$20</f>
+              <f>'DailyProfit'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$20</f>
+              <f>'DailyProfit'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$20</f>
+              <f>'DailyProfit'!$D$2:$D$21</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$20</f>
+              <f>'DailyProfit'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$20</f>
+              <f>'DailyProfit'!$F$2:$F$21</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$20</f>
+              <f>'DailyProfit'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$20</f>
+              <f>'DailyProfit'!$G$2:$G$21</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$20</f>
+              <f>'DailyProfit'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$20</f>
+              <f>'DailyProfit'!$H$2:$H$21</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1840,7 +1840,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
@@ -1871,6 +1871,40 @@
       </c>
       <c r="J20" s="11" t="n">
         <v>-10812165</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>333797</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>6056090</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>12050614</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>12600</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0.002649182539682539</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.04806420634920635</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>0.09563979365079366</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>-137383020</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>12050555</v>
       </c>
     </row>
   </sheetData>
@@ -1948,7 +1982,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1993,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>0</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="4">
@@ -1969,7 +2003,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>137716817</v>
+        <v>333797</v>
       </c>
     </row>
     <row r="5">
@@ -1979,7 +2013,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>9</v>
+        <v>6056090</v>
       </c>
     </row>
     <row r="6">
@@ -1989,7 +2023,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>59</v>
+        <v>12050614</v>
       </c>
     </row>
     <row r="7">
@@ -1999,7 +2033,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>34429204.25</v>
+        <v>0.002649182539682539</v>
       </c>
     </row>
     <row r="8">
@@ -2009,7 +2043,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>2.25</v>
+        <v>0.04806420634920635</v>
       </c>
     </row>
     <row r="9">
@@ -2019,7 +2053,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>14.75</v>
+        <v>0.09563979365079366</v>
       </c>
     </row>
     <row r="10">
@@ -2029,7 +2063,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>7441873.263157895</v>
+        <v>7086469.45</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$21</f>
+              <f>'DailyProfit'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$21</f>
+              <f>'DailyProfit'!$B$2:$B$22</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$21</f>
+              <f>'DailyProfit'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$21</f>
+              <f>'DailyProfit'!$D$2:$D$22</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$21</f>
+              <f>'DailyProfit'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$21</f>
+              <f>'DailyProfit'!$F$2:$F$22</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$21</f>
+              <f>'DailyProfit'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$21</f>
+              <f>'DailyProfit'!$G$2:$G$22</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$21</f>
+              <f>'DailyProfit'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$21</f>
+              <f>'DailyProfit'!$H$2:$H$22</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1874,7 +1874,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
@@ -1905,6 +1905,40 @@
       </c>
       <c r="J21" s="11" t="n">
         <v>12050555</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>359407</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>6415497</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>179703.5</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>3207748.5</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>-333737</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>-5635117</v>
       </c>
     </row>
   </sheetData>
@@ -1982,7 +2016,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -1993,7 +2027,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>12600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2003,7 +2037,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>333797</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -2013,7 +2047,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>6056090</v>
+        <v>359407</v>
       </c>
     </row>
     <row r="6">
@@ -2023,7 +2057,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>12050614</v>
+        <v>6415497</v>
       </c>
     </row>
     <row r="7">
@@ -2033,7 +2067,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.002649182539682539</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -2043,7 +2077,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.04806420634920635</v>
+        <v>179703.5</v>
       </c>
     </row>
     <row r="9">
@@ -2053,7 +2087,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.09563979365079366</v>
+        <v>3207748.5</v>
       </c>
     </row>
     <row r="10">
@@ -2063,7 +2097,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>7086469.45</v>
+        <v>6749021.380952381</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$22</f>
+              <f>'DailyProfit'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$22</f>
+              <f>'DailyProfit'!$B$2:$B$23</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$22</f>
+              <f>'DailyProfit'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$22</f>
+              <f>'DailyProfit'!$D$2:$D$23</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$22</f>
+              <f>'DailyProfit'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$22</f>
+              <f>'DailyProfit'!$F$2:$F$23</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$22</f>
+              <f>'DailyProfit'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$22</f>
+              <f>'DailyProfit'!$G$2:$G$23</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$22</f>
+              <f>'DailyProfit'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$22</f>
+              <f>'DailyProfit'!$H$2:$H$23</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1908,7 +1908,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
@@ -1939,6 +1939,40 @@
       </c>
       <c r="J22" s="11" t="n">
         <v>-5635117</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>134404</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>134404</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>67202</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>67202</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>-6281093</v>
       </c>
     </row>
   </sheetData>
@@ -2016,7 +2050,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2071,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -2047,7 +2081,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>359407</v>
+        <v>134404</v>
       </c>
     </row>
     <row r="6">
@@ -2057,7 +2091,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>6415497</v>
+        <v>134404</v>
       </c>
     </row>
     <row r="7">
@@ -2067,7 +2101,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>30</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="8">
@@ -2077,7 +2111,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>179703.5</v>
+        <v>67202</v>
       </c>
     </row>
     <row r="9">
@@ -2087,7 +2121,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>3207748.5</v>
+        <v>67202</v>
       </c>
     </row>
     <row r="10">
@@ -2097,7 +2131,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>6749021.380952381</v>
+        <v>6442250.363636363</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$23</f>
+              <f>'DailyProfit'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$23</f>
+              <f>'DailyProfit'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$23</f>
+              <f>'DailyProfit'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$23</f>
+              <f>'DailyProfit'!$D$2:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$23</f>
+              <f>'DailyProfit'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$23</f>
+              <f>'DailyProfit'!$F$2:$F$24</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$23</f>
+              <f>'DailyProfit'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$23</f>
+              <f>'DailyProfit'!$G$2:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$23</f>
+              <f>'DailyProfit'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$23</f>
+              <f>'DailyProfit'!$H$2:$H$24</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1942,7 +1942,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
@@ -1973,6 +1973,40 @@
       </c>
       <c r="J23" s="11" t="n">
         <v>-6281093</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>156474</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>290878</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>12700899</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>12600</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>0.001241857142857143</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.002308555555555555</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>0.1008007857142857</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>156415</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>12566495</v>
       </c>
     </row>
   </sheetData>
@@ -2050,7 +2084,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2095,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>0</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="4">
@@ -2071,7 +2105,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>59</v>
+        <v>156474</v>
       </c>
     </row>
     <row r="5">
@@ -2081,7 +2115,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>134404</v>
+        <v>290878</v>
       </c>
     </row>
     <row r="6">
@@ -2091,7 +2125,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>134404</v>
+        <v>12700899</v>
       </c>
     </row>
     <row r="7">
@@ -2101,7 +2135,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>29.5</v>
+        <v>0.001241857142857143</v>
       </c>
     </row>
     <row r="8">
@@ -2111,7 +2145,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>67202</v>
+        <v>0.002308555555555555</v>
       </c>
     </row>
     <row r="9">
@@ -2121,7 +2155,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>67202</v>
+        <v>0.1008007857142857</v>
       </c>
     </row>
     <row r="10">
@@ -2131,7 +2165,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>6442250.363636363</v>
+        <v>6168955.739130435</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$24</f>
+              <f>'DailyProfit'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$24</f>
+              <f>'DailyProfit'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$24</f>
+              <f>'DailyProfit'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$24</f>
+              <f>'DailyProfit'!$D$2:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$24</f>
+              <f>'DailyProfit'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$24</f>
+              <f>'DailyProfit'!$F$2:$F$25</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$24</f>
+              <f>'DailyProfit'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$24</f>
+              <f>'DailyProfit'!$G$2:$G$25</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$24</f>
+              <f>'DailyProfit'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$24</f>
+              <f>'DailyProfit'!$H$2:$H$25</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -1976,7 +1976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
@@ -2007,6 +2007,40 @@
       </c>
       <c r="J24" s="11" t="n">
         <v>12566495</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>107134</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>398012</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>12808033</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>12600</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>0.0008502698412698413</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.003158825396825397</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>0.1016510555555556</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>-49340</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>107134</v>
       </c>
     </row>
   </sheetData>
@@ -2084,7 +2118,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2139,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>156474</v>
+        <v>107134</v>
       </c>
     </row>
     <row r="5">
@@ -2115,7 +2149,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>290878</v>
+        <v>398012</v>
       </c>
     </row>
     <row r="6">
@@ -2125,7 +2159,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>12700899</v>
+        <v>12808033</v>
       </c>
     </row>
     <row r="7">
@@ -2135,7 +2169,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001241857142857143</v>
+        <v>0.0008502698412698413</v>
       </c>
     </row>
     <row r="8">
@@ -2145,7 +2179,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.002308555555555555</v>
+        <v>0.003158825396825397</v>
       </c>
     </row>
     <row r="9">
@@ -2155,7 +2189,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1008007857142857</v>
+        <v>0.1016510555555556</v>
       </c>
     </row>
     <row r="10">
@@ -2165,7 +2199,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>6168955.739130435</v>
+        <v>5916379.833333333</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$25</f>
+              <f>'DailyProfit'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$25</f>
+              <f>'DailyProfit'!$B$2:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$25</f>
+              <f>'DailyProfit'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$25</f>
+              <f>'DailyProfit'!$D$2:$D$26</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$25</f>
+              <f>'DailyProfit'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$25</f>
+              <f>'DailyProfit'!$F$2:$F$26</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$25</f>
+              <f>'DailyProfit'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$25</f>
+              <f>'DailyProfit'!$G$2:$G$26</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$25</f>
+              <f>'DailyProfit'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$25</f>
+              <f>'DailyProfit'!$H$2:$H$26</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2010,7 +2010,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
@@ -2041,6 +2041,40 @@
       </c>
       <c r="J25" s="11" t="n">
         <v>107134</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>187154</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>585166</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>12995187</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>12600</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>0.001485349206349206</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.004644174603174603</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>0.1031364047619048</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>80020</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>187154</v>
       </c>
     </row>
   </sheetData>
@@ -2118,7 +2152,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2173,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>107134</v>
+        <v>187154</v>
       </c>
     </row>
     <row r="5">
@@ -2149,7 +2183,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>398012</v>
+        <v>585166</v>
       </c>
     </row>
     <row r="6">
@@ -2159,7 +2193,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>12808033</v>
+        <v>12995187</v>
       </c>
     </row>
     <row r="7">
@@ -2169,7 +2203,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0008502698412698413</v>
+        <v>0.001485349206349206</v>
       </c>
     </row>
     <row r="8">
@@ -2179,7 +2213,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.003158825396825397</v>
+        <v>0.004644174603174603</v>
       </c>
     </row>
     <row r="9">
@@ -2189,7 +2223,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1016510555555556</v>
+        <v>0.1031364047619048</v>
       </c>
     </row>
     <row r="10">
@@ -2199,7 +2233,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>5916379.833333333</v>
+        <v>5687210.8</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$26</f>
+              <f>'DailyProfit'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$26</f>
+              <f>'DailyProfit'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$26</f>
+              <f>'DailyProfit'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$26</f>
+              <f>'DailyProfit'!$D$2:$D$27</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$26</f>
+              <f>'DailyProfit'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$26</f>
+              <f>'DailyProfit'!$F$2:$F$27</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$26</f>
+              <f>'DailyProfit'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$26</f>
+              <f>'DailyProfit'!$G$2:$G$27</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$26</f>
+              <f>'DailyProfit'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$26</f>
+              <f>'DailyProfit'!$H$2:$H$27</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2044,7 +2044,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
@@ -2075,6 +2075,40 @@
       </c>
       <c r="J26" s="11" t="n">
         <v>187154</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>200425</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>785591</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>13195612</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>12600</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0.001590674603174603</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.006234849206349207</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>0.1047270793650794</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>13271</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>200425</v>
       </c>
     </row>
   </sheetData>
@@ -2152,7 +2186,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2207,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>187154</v>
+        <v>200425</v>
       </c>
     </row>
     <row r="5">
@@ -2183,7 +2217,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>585166</v>
+        <v>785591</v>
       </c>
     </row>
     <row r="6">
@@ -2193,7 +2227,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>12995187</v>
+        <v>13195612</v>
       </c>
     </row>
     <row r="7">
@@ -2203,7 +2237,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001485349206349206</v>
+        <v>0.001590674603174603</v>
       </c>
     </row>
     <row r="8">
@@ -2213,7 +2247,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.004644174603174603</v>
+        <v>0.006234849206349207</v>
       </c>
     </row>
     <row r="9">
@@ -2223,7 +2257,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1031364047619048</v>
+        <v>0.1047270793650794</v>
       </c>
     </row>
     <row r="10">
@@ -2233,7 +2267,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>5687210.8</v>
+        <v>5476180.576923077</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$27</f>
+              <f>'DailyProfit'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$27</f>
+              <f>'DailyProfit'!$B$2:$B$28</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$27</f>
+              <f>'DailyProfit'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$27</f>
+              <f>'DailyProfit'!$D$2:$D$28</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$27</f>
+              <f>'DailyProfit'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$27</f>
+              <f>'DailyProfit'!$F$2:$F$28</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$27</f>
+              <f>'DailyProfit'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$27</f>
+              <f>'DailyProfit'!$G$2:$G$28</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$27</f>
+              <f>'DailyProfit'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$27</f>
+              <f>'DailyProfit'!$H$2:$H$28</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2078,7 +2078,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
@@ -2109,6 +2109,40 @@
       </c>
       <c r="J27" s="11" t="n">
         <v>200425</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>121091</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>121091</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>-200415</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>-13074521</v>
       </c>
     </row>
   </sheetData>
@@ -2186,7 +2220,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2231,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>12600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2207,7 +2241,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>200425</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2217,7 +2251,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>785591</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
@@ -2227,7 +2261,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>13195612</v>
+        <v>121091</v>
       </c>
     </row>
     <row r="7">
@@ -2237,7 +2271,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001590674603174603</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -2247,7 +2281,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.006234849206349207</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -2257,7 +2291,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1047270793650794</v>
+        <v>121091</v>
       </c>
     </row>
     <row r="10">
@@ -2267,7 +2301,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>5476180.576923077</v>
+        <v>5273359.444444444</v>
       </c>
     </row>
     <row r="11">
@@ -2300,7 +2334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2345,7 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$28</f>
+              <f>'DailyProfit'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$28</f>
+              <f>'DailyProfit'!$B$2:$B$29</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$28</f>
+              <f>'DailyProfit'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$28</f>
+              <f>'DailyProfit'!$D$2:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$28</f>
+              <f>'DailyProfit'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$28</f>
+              <f>'DailyProfit'!$F$2:$F$29</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$28</f>
+              <f>'DailyProfit'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$28</f>
+              <f>'DailyProfit'!$G$2:$G$29</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$28</f>
+              <f>'DailyProfit'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$28</f>
+              <f>'DailyProfit'!$H$2:$H$29</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2112,7 +2112,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
@@ -2143,6 +2143,40 @@
       </c>
       <c r="J28" s="11" t="n">
         <v>-13074521</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>172758</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>172758</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>51667</v>
       </c>
     </row>
   </sheetData>
@@ -2220,7 +2254,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2275,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -2261,7 +2295,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>121091</v>
+        <v>172758</v>
       </c>
     </row>
     <row r="7">
@@ -2271,7 +2305,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -2291,7 +2325,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>121091</v>
+        <v>172758</v>
       </c>
     </row>
     <row r="10">
@@ -2301,7 +2335,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>5273359.444444444</v>
+        <v>5085025.571428572</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$29</f>
+              <f>'DailyProfit'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$29</f>
+              <f>'DailyProfit'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$29</f>
+              <f>'DailyProfit'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$29</f>
+              <f>'DailyProfit'!$D$2:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$29</f>
+              <f>'DailyProfit'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$29</f>
+              <f>'DailyProfit'!$F$2:$F$30</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$29</f>
+              <f>'DailyProfit'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$29</f>
+              <f>'DailyProfit'!$G$2:$G$30</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$29</f>
+              <f>'DailyProfit'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$29</f>
+              <f>'DailyProfit'!$H$2:$H$30</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2146,7 +2146,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
@@ -2177,6 +2177,40 @@
       </c>
       <c r="J29" s="11" t="n">
         <v>51667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>267982</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>267982</v>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>95224</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2288,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2329,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>172758</v>
+        <v>267982</v>
       </c>
     </row>
     <row r="7">
@@ -2325,7 +2359,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>172758</v>
+        <v>267982</v>
       </c>
     </row>
     <row r="10">
@@ -2335,7 +2369,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>5085025.571428572</v>
+        <v>4909680.24137931</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$30</f>
+              <f>'DailyProfit'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$30</f>
+              <f>'DailyProfit'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$30</f>
+              <f>'DailyProfit'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$30</f>
+              <f>'DailyProfit'!$D$2:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$30</f>
+              <f>'DailyProfit'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$30</f>
+              <f>'DailyProfit'!$F$2:$F$31</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$30</f>
+              <f>'DailyProfit'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$30</f>
+              <f>'DailyProfit'!$G$2:$G$31</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$30</f>
+              <f>'DailyProfit'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$30</f>
+              <f>'DailyProfit'!$H$2:$H$31</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2180,7 +2180,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
@@ -2211,6 +2211,40 @@
       </c>
       <c r="J30" s="11" t="n">
         <v>95224</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>103650</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>1451072</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>13861093</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>0.0008495901639344263</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.01189403278688525</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>0.1136155163934426</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>103639</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>13593111</v>
       </c>
     </row>
   </sheetData>
@@ -2288,7 +2322,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2333,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>0</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="4">
@@ -2309,7 +2343,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>11</v>
+        <v>103650</v>
       </c>
     </row>
     <row r="5">
@@ -2319,7 +2353,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>59</v>
+        <v>1451072</v>
       </c>
     </row>
     <row r="6">
@@ -2329,7 +2363,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>267982</v>
+        <v>13861093</v>
       </c>
     </row>
     <row r="7">
@@ -2339,7 +2373,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>11</v>
+        <v>0.0008495901639344263</v>
       </c>
     </row>
     <row r="8">
@@ -2349,7 +2383,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>59</v>
+        <v>0.01189403278688525</v>
       </c>
     </row>
     <row r="9">
@@ -2359,7 +2393,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>267982</v>
+        <v>0.1136155163934426</v>
       </c>
     </row>
     <row r="10">
@@ -2369,7 +2403,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>4909680.24137931</v>
+        <v>4749479.233333333</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$31</f>
+              <f>'DailyProfit'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$31</f>
+              <f>'DailyProfit'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$31</f>
+              <f>'DailyProfit'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$31</f>
+              <f>'DailyProfit'!$D$2:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$31</f>
+              <f>'DailyProfit'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$31</f>
+              <f>'DailyProfit'!$F$2:$F$32</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$31</f>
+              <f>'DailyProfit'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$31</f>
+              <f>'DailyProfit'!$G$2:$G$32</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$31</f>
+              <f>'DailyProfit'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$31</f>
+              <f>'DailyProfit'!$H$2:$H$32</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2214,7 +2214,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
@@ -2245,6 +2245,40 @@
       </c>
       <c r="J31" s="11" t="n">
         <v>13593111</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>112237</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>1563309</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>13973330</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>0.0009199754098360655</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.01281400819672131</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>0.1145354918032787</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>8587</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>112237</v>
       </c>
     </row>
   </sheetData>
@@ -2322,7 +2356,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2377,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>103650</v>
+        <v>112237</v>
       </c>
     </row>
     <row r="5">
@@ -2353,7 +2387,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1451072</v>
+        <v>1563309</v>
       </c>
     </row>
     <row r="6">
@@ -2363,7 +2397,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>13861093</v>
+        <v>13973330</v>
       </c>
     </row>
     <row r="7">
@@ -2373,7 +2407,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0008495901639344263</v>
+        <v>0.0009199754098360655</v>
       </c>
     </row>
     <row r="8">
@@ -2383,7 +2417,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01189403278688525</v>
+        <v>0.01281400819672131</v>
       </c>
     </row>
     <row r="9">
@@ -2393,7 +2427,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1136155163934426</v>
+        <v>0.1145354918032787</v>
       </c>
     </row>
     <row r="10">
@@ -2403,7 +2437,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>4749479.233333333</v>
+        <v>4599890.774193549</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$32</f>
+              <f>'DailyProfit'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$32</f>
+              <f>'DailyProfit'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$32</f>
+              <f>'DailyProfit'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$32</f>
+              <f>'DailyProfit'!$D$2:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$32</f>
+              <f>'DailyProfit'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$32</f>
+              <f>'DailyProfit'!$F$2:$F$33</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$32</f>
+              <f>'DailyProfit'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$32</f>
+              <f>'DailyProfit'!$G$2:$G$33</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$32</f>
+              <f>'DailyProfit'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$32</f>
+              <f>'DailyProfit'!$H$2:$H$33</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2248,7 +2248,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
@@ -2279,6 +2279,40 @@
       </c>
       <c r="J32" s="11" t="n">
         <v>112237</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>344230</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>1907539</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>14317560</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>0.00282155737704918</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.01563556557377049</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>0.1173570491803279</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>231993</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>344230</v>
       </c>
     </row>
   </sheetData>
@@ -2356,7 +2390,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2411,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>112237</v>
+        <v>344230</v>
       </c>
     </row>
     <row r="5">
@@ -2387,7 +2421,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1563309</v>
+        <v>1907539</v>
       </c>
     </row>
     <row r="6">
@@ -2397,7 +2431,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>13973330</v>
+        <v>14317560</v>
       </c>
     </row>
     <row r="7">
@@ -2407,7 +2441,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0009199754098360655</v>
+        <v>0.00282155737704918</v>
       </c>
     </row>
     <row r="8">
@@ -2417,7 +2451,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01281400819672131</v>
+        <v>0.01563556557377049</v>
       </c>
     </row>
     <row r="9">
@@ -2427,7 +2461,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1145354918032787</v>
+        <v>0.1173570491803279</v>
       </c>
     </row>
     <row r="10">
@@ -2437,7 +2471,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>4599890.774193549</v>
+        <v>4466901.375</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$33</f>
+              <f>'DailyProfit'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$33</f>
+              <f>'DailyProfit'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$33</f>
+              <f>'DailyProfit'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$33</f>
+              <f>'DailyProfit'!$D$2:$D$34</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$33</f>
+              <f>'DailyProfit'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$33</f>
+              <f>'DailyProfit'!$F$2:$F$34</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$33</f>
+              <f>'DailyProfit'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$33</f>
+              <f>'DailyProfit'!$G$2:$G$34</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$33</f>
+              <f>'DailyProfit'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$33</f>
+              <f>'DailyProfit'!$H$2:$H$34</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2282,7 +2282,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
@@ -2313,6 +2313,40 @@
       </c>
       <c r="J33" s="11" t="n">
         <v>344230</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>137812</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>2045351</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>14455372</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>0.001129606557377049</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.01676517213114754</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>0.1184866557377049</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>-206418</v>
+      </c>
+      <c r="J34" s="11" t="n">
+        <v>137812</v>
       </c>
     </row>
   </sheetData>
@@ -2390,7 +2424,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2445,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>344230</v>
+        <v>137812</v>
       </c>
     </row>
     <row r="5">
@@ -2421,7 +2455,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1907539</v>
+        <v>2045351</v>
       </c>
     </row>
     <row r="6">
@@ -2431,7 +2465,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>14317560</v>
+        <v>14455372</v>
       </c>
     </row>
     <row r="7">
@@ -2441,7 +2475,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.00282155737704918</v>
+        <v>0.001129606557377049</v>
       </c>
     </row>
     <row r="8">
@@ -2451,7 +2485,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01563556557377049</v>
+        <v>0.01676517213114754</v>
       </c>
     </row>
     <row r="9">
@@ -2461,7 +2495,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1173570491803279</v>
+        <v>0.1184866557377049</v>
       </c>
     </row>
     <row r="10">
@@ -2471,7 +2505,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>4466901.375</v>
+        <v>4335716.848484849</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$34</f>
+              <f>'DailyProfit'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$34</f>
+              <f>'DailyProfit'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$34</f>
+              <f>'DailyProfit'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$34</f>
+              <f>'DailyProfit'!$D$2:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$34</f>
+              <f>'DailyProfit'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$34</f>
+              <f>'DailyProfit'!$F$2:$F$35</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$34</f>
+              <f>'DailyProfit'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$34</f>
+              <f>'DailyProfit'!$G$2:$G$35</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$34</f>
+              <f>'DailyProfit'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$34</f>
+              <f>'DailyProfit'!$H$2:$H$35</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2316,7 +2316,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
@@ -2347,6 +2347,40 @@
       </c>
       <c r="J34" s="11" t="n">
         <v>137812</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>223297</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>2268648</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>14678669</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>0.001830303278688525</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.01859547540983606</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>0.1203169590163934</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>85485</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>223297</v>
       </c>
     </row>
   </sheetData>
@@ -2424,7 +2458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2479,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>137812</v>
+        <v>223297</v>
       </c>
     </row>
     <row r="5">
@@ -2455,7 +2489,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2045351</v>
+        <v>2268648</v>
       </c>
     </row>
     <row r="6">
@@ -2465,7 +2499,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>14455372</v>
+        <v>14678669</v>
       </c>
     </row>
     <row r="7">
@@ -2475,7 +2509,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001129606557377049</v>
+        <v>0.001830303278688525</v>
       </c>
     </row>
     <row r="8">
@@ -2485,7 +2519,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01676517213114754</v>
+        <v>0.01859547540983606</v>
       </c>
     </row>
     <row r="9">
@@ -2495,7 +2529,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1184866557377049</v>
+        <v>0.1203169590163934</v>
       </c>
     </row>
     <row r="10">
@@ -2505,7 +2539,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>4335716.848484849</v>
+        <v>4214763.323529412</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$35</f>
+              <f>'DailyProfit'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$35</f>
+              <f>'DailyProfit'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$35</f>
+              <f>'DailyProfit'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$35</f>
+              <f>'DailyProfit'!$D$2:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$35</f>
+              <f>'DailyProfit'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$35</f>
+              <f>'DailyProfit'!$F$2:$F$36</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$35</f>
+              <f>'DailyProfit'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$35</f>
+              <f>'DailyProfit'!$G$2:$G$36</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$35</f>
+              <f>'DailyProfit'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$35</f>
+              <f>'DailyProfit'!$H$2:$H$36</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2350,7 +2350,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
@@ -2381,6 +2381,40 @@
       </c>
       <c r="J35" s="11" t="n">
         <v>223297</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>189093</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>2457741</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>14867762</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>0.00154994262295082</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.02014541803278689</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>0.1218669016393443</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>-34204</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>189093</v>
       </c>
     </row>
   </sheetData>
@@ -2458,7 +2492,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2513,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>223297</v>
+        <v>189093</v>
       </c>
     </row>
     <row r="5">
@@ -2489,7 +2523,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2268648</v>
+        <v>2457741</v>
       </c>
     </row>
     <row r="6">
@@ -2499,7 +2533,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>14678669</v>
+        <v>14867762</v>
       </c>
     </row>
     <row r="7">
@@ -2509,7 +2543,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001830303278688525</v>
+        <v>0.00154994262295082</v>
       </c>
     </row>
     <row r="8">
@@ -2519,7 +2553,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01859547540983606</v>
+        <v>0.02014541803278689</v>
       </c>
     </row>
     <row r="9">
@@ -2529,7 +2563,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1203169590163934</v>
+        <v>0.1218669016393443</v>
       </c>
     </row>
     <row r="10">
@@ -2539,7 +2573,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>4214763.323529412</v>
+        <v>4099744.171428571</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$36</f>
+              <f>'DailyProfit'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$36</f>
+              <f>'DailyProfit'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$36</f>
+              <f>'DailyProfit'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$36</f>
+              <f>'DailyProfit'!$D$2:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$36</f>
+              <f>'DailyProfit'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$36</f>
+              <f>'DailyProfit'!$F$2:$F$37</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$36</f>
+              <f>'DailyProfit'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$36</f>
+              <f>'DailyProfit'!$G$2:$G$37</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$36</f>
+              <f>'DailyProfit'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$36</f>
+              <f>'DailyProfit'!$H$2:$H$37</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2384,7 +2384,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
@@ -2415,6 +2415,40 @@
       </c>
       <c r="J36" s="11" t="n">
         <v>189093</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>231816</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>2689557</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>15099578</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>0.001900131147540984</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.02204554918032787</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>0.1237670327868853</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>42723</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>231816</v>
       </c>
     </row>
   </sheetData>
@@ -2492,7 +2526,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2547,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>189093</v>
+        <v>231816</v>
       </c>
     </row>
     <row r="5">
@@ -2523,7 +2557,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2457741</v>
+        <v>2689557</v>
       </c>
     </row>
     <row r="6">
@@ -2533,7 +2567,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>14867762</v>
+        <v>15099578</v>
       </c>
     </row>
     <row r="7">
@@ -2543,7 +2577,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.00154994262295082</v>
+        <v>0.001900131147540984</v>
       </c>
     </row>
     <row r="8">
@@ -2553,7 +2587,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02014541803278689</v>
+        <v>0.02204554918032787</v>
       </c>
     </row>
     <row r="9">
@@ -2563,7 +2597,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1218669016393443</v>
+        <v>0.1237670327868853</v>
       </c>
     </row>
     <row r="10">
@@ -2573,7 +2607,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>4099744.171428571</v>
+        <v>3992301.722222222</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$37</f>
+              <f>'DailyProfit'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$37</f>
+              <f>'DailyProfit'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$37</f>
+              <f>'DailyProfit'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$37</f>
+              <f>'DailyProfit'!$D$2:$D$38</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$37</f>
+              <f>'DailyProfit'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$37</f>
+              <f>'DailyProfit'!$F$2:$F$38</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$37</f>
+              <f>'DailyProfit'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$37</f>
+              <f>'DailyProfit'!$G$2:$G$38</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$37</f>
+              <f>'DailyProfit'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$37</f>
+              <f>'DailyProfit'!$H$2:$H$38</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2418,7 +2418,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
@@ -2449,6 +2449,40 @@
       </c>
       <c r="J37" s="11" t="n">
         <v>231816</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>249607</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>2939164</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>15349185</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>0.002045959016393443</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.02409150819672131</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>0.1258129918032787</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>17791</v>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>249607</v>
       </c>
     </row>
   </sheetData>
@@ -2526,7 +2560,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2581,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>231816</v>
+        <v>249607</v>
       </c>
     </row>
     <row r="5">
@@ -2557,7 +2591,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2689557</v>
+        <v>2939164</v>
       </c>
     </row>
     <row r="6">
@@ -2567,7 +2601,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>15099578</v>
+        <v>15349185</v>
       </c>
     </row>
     <row r="7">
@@ -2577,7 +2611,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001900131147540984</v>
+        <v>0.002045959016393443</v>
       </c>
     </row>
     <row r="8">
@@ -2587,7 +2621,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02204554918032787</v>
+        <v>0.02409150819672131</v>
       </c>
     </row>
     <row r="9">
@@ -2597,7 +2631,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1237670327868853</v>
+        <v>0.1258129918032787</v>
       </c>
     </row>
     <row r="10">
@@ -2607,7 +2641,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3992301.722222222</v>
+        <v>3891147.810810811</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$38</f>
+              <f>'DailyProfit'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$38</f>
+              <f>'DailyProfit'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$38</f>
+              <f>'DailyProfit'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$38</f>
+              <f>'DailyProfit'!$D$2:$D$39</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$38</f>
+              <f>'DailyProfit'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$38</f>
+              <f>'DailyProfit'!$F$2:$F$39</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$38</f>
+              <f>'DailyProfit'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$38</f>
+              <f>'DailyProfit'!$G$2:$G$39</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$38</f>
+              <f>'DailyProfit'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$38</f>
+              <f>'DailyProfit'!$H$2:$H$39</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2452,7 +2452,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
@@ -2483,6 +2483,40 @@
       </c>
       <c r="J38" s="11" t="n">
         <v>249607</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>133614</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>133614</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>-249595</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>-15215571</v>
       </c>
     </row>
   </sheetData>
@@ -2560,7 +2594,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2605,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>12200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2581,7 +2615,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>249607</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -2591,7 +2625,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2939164</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -2601,7 +2635,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>15349185</v>
+        <v>133614</v>
       </c>
     </row>
     <row r="7">
@@ -2611,7 +2645,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.002045959016393443</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -2621,7 +2655,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02409150819672131</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -2631,7 +2665,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1258129918032787</v>
+        <v>133614</v>
       </c>
     </row>
     <row r="10">
@@ -2641,7 +2675,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3891147.810810811</v>
+        <v>3788749.5</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$39</f>
+              <f>'DailyProfit'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$39</f>
+              <f>'DailyProfit'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$39</f>
+              <f>'DailyProfit'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$39</f>
+              <f>'DailyProfit'!$D$2:$D$40</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$39</f>
+              <f>'DailyProfit'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$39</f>
+              <f>'DailyProfit'!$F$2:$F$40</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$39</f>
+              <f>'DailyProfit'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$39</f>
+              <f>'DailyProfit'!$G$2:$G$40</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$39</f>
+              <f>'DailyProfit'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$39</f>
+              <f>'DailyProfit'!$H$2:$H$40</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2486,7 +2486,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
@@ -2517,6 +2517,40 @@
       </c>
       <c r="J39" s="11" t="n">
         <v>-15215571</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>189478</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>3454382</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>15864403</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>0.001553098360655738</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0.02831460655737705</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>0.1300360901639344</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>189466</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>15730789</v>
       </c>
     </row>
   </sheetData>
@@ -2594,7 +2628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2639,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>0</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="4">
@@ -2615,7 +2649,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>12</v>
+        <v>189478</v>
       </c>
     </row>
     <row r="5">
@@ -2625,7 +2659,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>58</v>
+        <v>3454382</v>
       </c>
     </row>
     <row r="6">
@@ -2635,7 +2669,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>133614</v>
+        <v>15864403</v>
       </c>
     </row>
     <row r="7">
@@ -2645,7 +2679,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>12</v>
+        <v>0.001553098360655738</v>
       </c>
     </row>
     <row r="8">
@@ -2655,7 +2689,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>58</v>
+        <v>0.02831460655737705</v>
       </c>
     </row>
     <row r="9">
@@ -2665,7 +2699,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>133614</v>
+        <v>0.1300360901639344</v>
       </c>
     </row>
     <row r="10">
@@ -2675,7 +2709,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3788749.5</v>
+        <v>3696460.487179487</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$40</f>
+              <f>'DailyProfit'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$40</f>
+              <f>'DailyProfit'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$40</f>
+              <f>'DailyProfit'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$40</f>
+              <f>'DailyProfit'!$D$2:$D$41</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$40</f>
+              <f>'DailyProfit'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$40</f>
+              <f>'DailyProfit'!$F$2:$F$41</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$40</f>
+              <f>'DailyProfit'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$40</f>
+              <f>'DailyProfit'!$G$2:$G$41</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$40</f>
+              <f>'DailyProfit'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$40</f>
+              <f>'DailyProfit'!$H$2:$H$41</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2520,7 +2520,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -2551,6 +2551,40 @@
       </c>
       <c r="J40" s="11" t="n">
         <v>15730789</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>94802</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>94802</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>15959205</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>0.0007770655737704918</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0.0007770655737704918</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>0.1308131557377049</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>-94676</v>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>94802</v>
       </c>
     </row>
   </sheetData>
@@ -2628,7 +2662,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2683,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>189478</v>
+        <v>94802</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2693,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>3454382</v>
+        <v>94802</v>
       </c>
     </row>
     <row r="6">
@@ -2669,7 +2703,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>15864403</v>
+        <v>15959205</v>
       </c>
     </row>
     <row r="7">
@@ -2679,7 +2713,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001553098360655738</v>
+        <v>0.0007770655737704918</v>
       </c>
     </row>
     <row r="8">
@@ -2689,7 +2723,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02831460655737705</v>
+        <v>0.0007770655737704918</v>
       </c>
     </row>
     <row r="9">
@@ -2699,7 +2733,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1300360901639344</v>
+        <v>0.1308131557377049</v>
       </c>
     </row>
     <row r="10">
@@ -2709,7 +2743,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3696460.487179487</v>
+        <v>3606419.025</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$41</f>
+              <f>'DailyProfit'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$41</f>
+              <f>'DailyProfit'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$41</f>
+              <f>'DailyProfit'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$41</f>
+              <f>'DailyProfit'!$D$2:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$41</f>
+              <f>'DailyProfit'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$41</f>
+              <f>'DailyProfit'!$F$2:$F$42</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$41</f>
+              <f>'DailyProfit'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$41</f>
+              <f>'DailyProfit'!$G$2:$G$42</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$41</f>
+              <f>'DailyProfit'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$41</f>
+              <f>'DailyProfit'!$H$2:$H$42</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2554,7 +2554,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
@@ -2585,6 +2585,40 @@
       </c>
       <c r="J41" s="11" t="n">
         <v>94802</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>92093</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>186895</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>16051298</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>10700</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>0.0008606822429906542</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.001746682242990654</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>0.1500121308411215</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>-2709</v>
+      </c>
+      <c r="J42" s="11" t="n">
+        <v>92093</v>
       </c>
     </row>
   </sheetData>
@@ -2662,7 +2696,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2707,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>12200</v>
+        <v>10700</v>
       </c>
     </row>
     <row r="4">
@@ -2683,7 +2717,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>94802</v>
+        <v>92093</v>
       </c>
     </row>
     <row r="5">
@@ -2693,7 +2727,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>94802</v>
+        <v>186895</v>
       </c>
     </row>
     <row r="6">
@@ -2703,7 +2737,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>15959205</v>
+        <v>16051298</v>
       </c>
     </row>
     <row r="7">
@@ -2713,7 +2747,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0007770655737704918</v>
+        <v>0.0008606822429906542</v>
       </c>
     </row>
     <row r="8">
@@ -2723,7 +2757,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.0007770655737704918</v>
+        <v>0.001746682242990654</v>
       </c>
     </row>
     <row r="9">
@@ -2733,7 +2767,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1308131557377049</v>
+        <v>0.1500121308411215</v>
       </c>
     </row>
     <row r="10">
@@ -2743,7 +2777,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3606419.025</v>
+        <v>3520703.756097561</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$42</f>
+              <f>'DailyProfit'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$42</f>
+              <f>'DailyProfit'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$42</f>
+              <f>'DailyProfit'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$42</f>
+              <f>'DailyProfit'!$D$2:$D$43</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$42</f>
+              <f>'DailyProfit'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$42</f>
+              <f>'DailyProfit'!$F$2:$F$43</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$42</f>
+              <f>'DailyProfit'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$42</f>
+              <f>'DailyProfit'!$G$2:$G$43</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$42</f>
+              <f>'DailyProfit'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$42</f>
+              <f>'DailyProfit'!$H$2:$H$43</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2588,7 +2588,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
@@ -2619,6 +2619,40 @@
       </c>
       <c r="J42" s="11" t="n">
         <v>92093</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>160843</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>347738</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>16212141</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>10700</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>0.001503205607476635</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.00324988785046729</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>0.1515153364485981</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>68750</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>160843</v>
       </c>
     </row>
   </sheetData>
@@ -2696,7 +2730,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2751,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>92093</v>
+        <v>160843</v>
       </c>
     </row>
     <row r="5">
@@ -2727,7 +2761,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>186895</v>
+        <v>347738</v>
       </c>
     </row>
     <row r="6">
@@ -2737,7 +2771,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>16051298</v>
+        <v>16212141</v>
       </c>
     </row>
     <row r="7">
@@ -2747,7 +2781,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0008606822429906542</v>
+        <v>0.001503205607476635</v>
       </c>
     </row>
     <row r="8">
@@ -2757,7 +2791,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.001746682242990654</v>
+        <v>0.00324988785046729</v>
       </c>
     </row>
     <row r="9">
@@ -2767,7 +2801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1500121308411215</v>
+        <v>0.1515153364485981</v>
       </c>
     </row>
     <row r="10">
@@ -2777,7 +2811,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3520703.756097561</v>
+        <v>3440707.071428571</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$43</f>
+              <f>'DailyProfit'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$43</f>
+              <f>'DailyProfit'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$43</f>
+              <f>'DailyProfit'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$43</f>
+              <f>'DailyProfit'!$D$2:$D$44</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$43</f>
+              <f>'DailyProfit'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$43</f>
+              <f>'DailyProfit'!$F$2:$F$44</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$43</f>
+              <f>'DailyProfit'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$43</f>
+              <f>'DailyProfit'!$G$2:$G$44</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$43</f>
+              <f>'DailyProfit'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$43</f>
+              <f>'DailyProfit'!$H$2:$H$44</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2622,7 +2622,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
@@ -2653,6 +2653,40 @@
       </c>
       <c r="J43" s="11" t="n">
         <v>160843</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>110609</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>458347</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>16322750</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>10700</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>0.001033728971962617</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.004283616822429907</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>0.1525490654205607</v>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>-50234</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>110609</v>
       </c>
     </row>
   </sheetData>
@@ -2730,7 +2764,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2785,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>160843</v>
+        <v>110609</v>
       </c>
     </row>
     <row r="5">
@@ -2761,7 +2795,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>347738</v>
+        <v>458347</v>
       </c>
     </row>
     <row r="6">
@@ -2771,7 +2805,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>16212141</v>
+        <v>16322750</v>
       </c>
     </row>
     <row r="7">
@@ -2781,7 +2815,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001503205607476635</v>
+        <v>0.001033728971962617</v>
       </c>
     </row>
     <row r="8">
@@ -2791,7 +2825,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.00324988785046729</v>
+        <v>0.004283616822429907</v>
       </c>
     </row>
     <row r="9">
@@ -2801,7 +2835,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1515153364485981</v>
+        <v>0.1525490654205607</v>
       </c>
     </row>
     <row r="10">
@@ -2811,7 +2845,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3440707.071428571</v>
+        <v>3363262.930232558</v>
       </c>
     </row>
     <row r="11">
